--- a/fa25veggrow2.xlsx
+++ b/fa25veggrow2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37C2520A-AF88-45C8-A460-618C343450F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAD0708-6815-45B7-92CC-EA609E1DA442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{FAC64A56-71D4-4693-9441-3A1623B49342}"/>
   </bookViews>
@@ -47,12 +47,6 @@
     <t>Plant_ID</t>
   </si>
   <si>
-    <t>V_E</t>
-  </si>
-  <si>
-    <t>V_C</t>
-  </si>
-  <si>
     <t>V_1</t>
   </si>
   <si>
@@ -237,6 +231,12 @@
   </si>
   <si>
     <t>Microplastic</t>
+  </si>
+  <si>
+    <t>V_17</t>
+  </si>
+  <si>
+    <t>V_18</t>
   </si>
 </sst>
 </file>
@@ -679,21 +679,21 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
       </c>
       <c r="D2">
         <v>0.42857142857142855</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
       </c>
       <c r="D3">
         <v>0.42857142857142855</v>
@@ -790,13 +790,13 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>0.42857142857142855</v>
@@ -840,13 +840,13 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>0.42857142857142855</v>
@@ -896,13 +896,13 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>0.5714285714285714</v>
@@ -946,13 +946,13 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>0.42857142857142855</v>
@@ -999,13 +999,13 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8">
         <v>0.42857142857142855</v>
@@ -1055,13 +1055,13 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>0.5714285714285714</v>
@@ -1108,13 +1108,13 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>0.42857142857142855</v>
@@ -1161,13 +1161,13 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
       </c>
       <c r="D11">
         <v>0.5714285714285714</v>
@@ -1217,13 +1217,13 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <v>0.42857142857142855</v>
@@ -1273,13 +1273,13 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>0.5714285714285714</v>
@@ -1326,13 +1326,13 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>0.42857142857142855</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>0.5714285714285714</v>
@@ -1432,13 +1432,13 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>0.42857142857142855</v>
@@ -1485,13 +1485,13 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17">
         <v>0.5714285714285714</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D18">
         <v>0.5714285714285714</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19">
         <v>0.5714285714285714</v>
@@ -1641,13 +1641,13 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D20">
         <v>0.42857142857142855</v>
@@ -1691,13 +1691,13 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21">
         <v>0.42857142857142855</v>
@@ -1744,13 +1744,13 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D22">
         <v>0.5714285714285714</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D23">
         <v>0.42857142857142855</v>
@@ -1850,13 +1850,13 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24">
         <v>0.5714285714285714</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D25">
         <v>0.5714285714285714</v>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D26">
         <v>0.7142857142857143</v>
@@ -2018,13 +2018,13 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D27">
         <v>0.5714285714285714</v>
@@ -2074,13 +2074,13 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D28">
         <v>0.5714285714285714</v>
@@ -2130,13 +2130,13 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D29">
         <v>0.5714285714285714</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D30">
         <v>0.5714285714285714</v>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D31">
         <v>0.5714285714285714</v>
@@ -2307,13 +2307,13 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D32">
         <v>0.5714285714285714</v>
@@ -2360,13 +2360,13 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>0.42857142857142855</v>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D34">
         <v>0.5714285714285714</v>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D35">
         <v>0.42857142857142855</v>
@@ -2522,13 +2522,13 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D36">
         <v>0.5714285714285714</v>
@@ -2578,13 +2578,13 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D37">
         <v>0.5714285714285714</v>
@@ -2634,13 +2634,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D38">
         <v>0.5714285714285714</v>
@@ -2693,13 +2693,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D39">
         <v>0.5714285714285714</v>
@@ -2749,13 +2749,13 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D40">
         <v>0.5714285714285714</v>
@@ -2808,13 +2808,13 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D41">
         <v>0.42857142857142855</v>
@@ -2867,13 +2867,13 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D42">
         <v>0.5714285714285714</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D43">
         <v>0.5714285714285714</v>

--- a/fa25veggrow2.xlsx
+++ b/fa25veggrow2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAD0708-6815-45B7-92CC-EA609E1DA442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7F721C-D62F-4512-B9C5-58A2E8EFCB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{FAC64A56-71D4-4693-9441-3A1623B49342}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{FAC64A56-71D4-4693-9441-3A1623B49342}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="66">
   <si>
     <t>Treatment</t>
   </si>
   <si>
-    <t>Beetles</t>
-  </si>
-  <si>
     <t>Plant_ID</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
     <t>Control</t>
   </si>
   <si>
-    <t>n</t>
-  </si>
-  <si>
     <t>C-Sb-1</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t>C-Sb-8</t>
   </si>
   <si>
-    <t>y</t>
-  </si>
-  <si>
     <t>C-MBB-1</t>
   </si>
   <si>
@@ -237,6 +228,12 @@
   </si>
   <si>
     <t>V_18</t>
+  </si>
+  <si>
+    <t>Beetle</t>
+  </si>
+  <si>
+    <t>No Beetle</t>
   </si>
 </sst>
 </file>
@@ -625,75 +622,75 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
       <c r="T1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="U1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
       </c>
       <c r="D2">
         <v>0.42857142857142855</v>
@@ -737,13 +734,13 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
       </c>
       <c r="D3">
         <v>0.42857142857142855</v>
@@ -790,13 +787,13 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>0.42857142857142855</v>
@@ -840,13 +837,13 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>0.42857142857142855</v>
@@ -896,13 +893,13 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>0.5714285714285714</v>
@@ -946,13 +943,13 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>0.42857142857142855</v>
@@ -999,13 +996,13 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>0.42857142857142855</v>
@@ -1055,13 +1052,13 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>0.5714285714285714</v>
@@ -1108,13 +1105,13 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>0.42857142857142855</v>
@@ -1161,13 +1158,13 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>0.5714285714285714</v>
@@ -1217,13 +1214,13 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
       </c>
       <c r="D12">
         <v>0.42857142857142855</v>
@@ -1273,13 +1270,13 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>0.5714285714285714</v>
@@ -1326,13 +1323,13 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>0.42857142857142855</v>
@@ -1379,13 +1376,13 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D15">
         <v>0.5714285714285714</v>
@@ -1432,13 +1429,13 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>0.42857142857142855</v>
@@ -1485,13 +1482,13 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D17">
         <v>0.5714285714285714</v>
@@ -1532,13 +1529,13 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D18">
         <v>0.5714285714285714</v>
@@ -1588,13 +1585,13 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D19">
         <v>0.5714285714285714</v>
@@ -1641,13 +1638,13 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D20">
         <v>0.42857142857142855</v>
@@ -1691,13 +1688,13 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D21">
         <v>0.42857142857142855</v>
@@ -1744,13 +1741,13 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D22">
         <v>0.5714285714285714</v>
@@ -1794,13 +1791,13 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D23">
         <v>0.42857142857142855</v>
@@ -1850,13 +1847,13 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D24">
         <v>0.5714285714285714</v>
@@ -1906,13 +1903,13 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D25">
         <v>0.5714285714285714</v>
@@ -1962,13 +1959,13 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D26">
         <v>0.7142857142857143</v>
@@ -2018,13 +2015,13 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D27">
         <v>0.5714285714285714</v>
@@ -2074,13 +2071,13 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D28">
         <v>0.5714285714285714</v>
@@ -2130,13 +2127,13 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D29">
         <v>0.5714285714285714</v>
@@ -2195,13 +2192,13 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D30">
         <v>0.5714285714285714</v>
@@ -2251,13 +2248,13 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="s">
-        <v>29</v>
-      </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D31">
         <v>0.5714285714285714</v>
@@ -2307,13 +2304,13 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
         <v>64</v>
       </c>
-      <c r="B32" t="s">
-        <v>29</v>
-      </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D32">
         <v>0.5714285714285714</v>
@@ -2360,13 +2357,13 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
         <v>64</v>
       </c>
-      <c r="B33" t="s">
-        <v>29</v>
-      </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D33">
         <v>0.42857142857142855</v>
@@ -2413,13 +2410,13 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
         <v>64</v>
       </c>
-      <c r="B34" t="s">
-        <v>29</v>
-      </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D34">
         <v>0.5714285714285714</v>
@@ -2469,13 +2466,13 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" t="s">
         <v>64</v>
       </c>
-      <c r="B35" t="s">
-        <v>29</v>
-      </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D35">
         <v>0.42857142857142855</v>
@@ -2522,13 +2519,13 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s">
         <v>64</v>
       </c>
-      <c r="B36" t="s">
-        <v>29</v>
-      </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D36">
         <v>0.5714285714285714</v>
@@ -2578,13 +2575,13 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" t="s">
         <v>64</v>
       </c>
-      <c r="B37" t="s">
-        <v>29</v>
-      </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D37">
         <v>0.5714285714285714</v>
@@ -2634,13 +2631,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
         <v>64</v>
       </c>
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D38">
         <v>0.5714285714285714</v>
@@ -2693,13 +2690,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D39">
         <v>0.5714285714285714</v>
@@ -2749,13 +2746,13 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>0.5714285714285714</v>
@@ -2808,13 +2805,13 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D41">
         <v>0.42857142857142855</v>
@@ -2867,13 +2864,13 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D42">
         <v>0.5714285714285714</v>
@@ -2926,13 +2923,13 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D43">
         <v>0.5714285714285714</v>
